--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
           <t>PnL_R$</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro_Green_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -615,6 +620,7 @@
       <c r="T2" t="n">
         <v>5</v>
       </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -624,37 +630,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CYPRUS 1</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pafos FC x Olympiakos Nicosia FC</t>
+          <t>Asteras Tripolis x Iraklis</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olympiakos Nicosia FC</t>
+          <t>Iraklis</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -663,43 +669,42 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5.7</v>
+        <v>25</v>
       </c>
       <c r="K3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>21.28</v>
+        <v>8.33</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>-4.7</v>
-      </c>
       <c r="T3" t="n">
-        <v>-100</v>
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -710,27 +715,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ISRAEL 1</t>
+          <t>CYPRUS 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv x Hapoel Ramat Gan</t>
+          <t>Pafos FC x Olympiakos Nicosia FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Olympiakos Nicosia FC</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -749,44 +754,45 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="L4" t="n">
-        <v>20.41</v>
+        <v>21.28</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.95</v>
+        <v>-4.7</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.95</v>
+        <v>-4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>19.39</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -796,27 +802,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>ISRAEL 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Al-Hilal x NEOM Sports Club</t>
+          <t>Hapoel Tel Aviv x Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -835,20 +841,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="L5" t="n">
-        <v>14.71</v>
+        <v>20.41</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -871,8 +877,9 @@
         <v>0.95</v>
       </c>
       <c r="T5" t="n">
-        <v>13.97</v>
-      </c>
+        <v>19.39</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -882,37 +889,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nueva Chicago x Quilmes</t>
+          <t>National Bank Egypt x Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>National Bank Egypt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -921,20 +928,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5.56</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -945,20 +952,280 @@
       <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="T6" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EGYPT 1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>National Bank x Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>National Bank</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ghazl El Mahallah</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>21</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="n">
+        <v>200</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SAUDI ARABIA 1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Al-Hilal x NEOM Sports Club</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Al-Hilal</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NEOM Sports Club</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="M8" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0.95</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="S8" t="n">
         <v>0.95</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T8" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ARGENTINA 2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Nueva Chicago x Quilmes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Over 4.5 FT</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>19</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="M9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1x0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T9" t="n">
         <v>5.28</v>
       </c>
+      <c r="U9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -682,12 +682,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -682,12 +682,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -682,19 +682,19 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -1028,19 +1028,19 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S7" t="n">
